--- a/artfynd/A 31821-2025 artfynd.xlsx
+++ b/artfynd/A 31821-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126580324</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126580843</v>
       </c>
       <c r="B3" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126580437</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126580446</v>
       </c>
       <c r="B5" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126580440</v>
       </c>
       <c r="B6" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>126580523</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>126580323</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>126580448</v>
       </c>
       <c r="B9" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>126580445</v>
       </c>
       <c r="B10" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>126580447</v>
       </c>
       <c r="B11" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126580522</v>
+        <v>126580811</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>91580</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>967</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386316</v>
+        <v>386318</v>
       </c>
       <c r="R12" t="n">
-        <v>6842407</v>
+        <v>6842423</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126580811</v>
+        <v>126580522</v>
       </c>
       <c r="B13" t="n">
-        <v>91506</v>
+        <v>79106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>967</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386318</v>
+        <v>386316</v>
       </c>
       <c r="R13" t="n">
-        <v>6842423</v>
+        <v>6842407</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>126580322</v>
       </c>
       <c r="B14" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 31821-2025 artfynd.xlsx
+++ b/artfynd/A 31821-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126580324</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126580843</v>
+        <v>126580437</v>
       </c>
       <c r="B3" t="n">
-        <v>78417</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386302</v>
+        <v>386276</v>
       </c>
       <c r="R3" t="n">
-        <v>6842401</v>
+        <v>6842371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126580437</v>
+        <v>126580843</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>78420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386276</v>
+        <v>386302</v>
       </c>
       <c r="R4" t="n">
-        <v>6842371</v>
+        <v>6842401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>126580446</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126580440</v>
       </c>
       <c r="B6" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>126580523</v>
       </c>
       <c r="B7" t="n">
-        <v>79106</v>
+        <v>79109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>126580323</v>
       </c>
       <c r="B8" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>126580448</v>
       </c>
       <c r="B9" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>126580445</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>126580447</v>
       </c>
       <c r="B11" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126580811</v>
+        <v>126580522</v>
       </c>
       <c r="B12" t="n">
-        <v>91580</v>
+        <v>79109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>967</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386318</v>
+        <v>386316</v>
       </c>
       <c r="R12" t="n">
-        <v>6842423</v>
+        <v>6842407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126580522</v>
+        <v>126580811</v>
       </c>
       <c r="B13" t="n">
-        <v>79106</v>
+        <v>91586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>967</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386316</v>
+        <v>386318</v>
       </c>
       <c r="R13" t="n">
-        <v>6842407</v>
+        <v>6842423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>126580322</v>
       </c>
       <c r="B14" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 31821-2025 artfynd.xlsx
+++ b/artfynd/A 31821-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126580324</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126580437</v>
+        <v>126580843</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>78417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386276</v>
+        <v>386302</v>
       </c>
       <c r="R3" t="n">
-        <v>6842371</v>
+        <v>6842401</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126580843</v>
+        <v>126580437</v>
       </c>
       <c r="B4" t="n">
-        <v>78420</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386302</v>
+        <v>386276</v>
       </c>
       <c r="R4" t="n">
-        <v>6842401</v>
+        <v>6842371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>126580446</v>
       </c>
       <c r="B5" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126580440</v>
       </c>
       <c r="B6" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>126580523</v>
       </c>
       <c r="B7" t="n">
-        <v>79109</v>
+        <v>79106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>126580323</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>126580448</v>
       </c>
       <c r="B9" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>126580445</v>
       </c>
       <c r="B10" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>126580447</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126580522</v>
+        <v>126580811</v>
       </c>
       <c r="B12" t="n">
-        <v>79109</v>
+        <v>91580</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>967</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386316</v>
+        <v>386318</v>
       </c>
       <c r="R12" t="n">
-        <v>6842407</v>
+        <v>6842423</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126580811</v>
+        <v>126580522</v>
       </c>
       <c r="B13" t="n">
-        <v>91586</v>
+        <v>79106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>967</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386318</v>
+        <v>386316</v>
       </c>
       <c r="R13" t="n">
-        <v>6842423</v>
+        <v>6842407</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>126580322</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 31821-2025 artfynd.xlsx
+++ b/artfynd/A 31821-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580522</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580523</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580843</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580691</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580322</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580323</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580324</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580437</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580613</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580440</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580445</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580446</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580447</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580448</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,8 +2314,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126580449</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>